--- a/配置表格/J技能BUFF表.xlsx
+++ b/配置表格/J技能BUFF表.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="551">
   <si>
     <t>##var</t>
   </si>
@@ -116,6 +116,9 @@
     <t>skill_selector</t>
   </si>
   <si>
+    <t>sub_selector</t>
+  </si>
+  <si>
     <t>damage_type</t>
   </si>
   <si>
@@ -152,6 +155,21 @@
     <t>cooldown_reduction_disabled</t>
   </si>
   <si>
+    <t>max_charges</t>
+  </si>
+  <si>
+    <t>charge_recover_time</t>
+  </si>
+  <si>
+    <t>channel_time</t>
+  </si>
+  <si>
+    <t>channel_interval</t>
+  </si>
+  <si>
+    <t>channel_move_cancel</t>
+  </si>
+  <si>
     <t>hit_stun</t>
   </si>
   <si>
@@ -197,9 +215,15 @@
     <t>SkillSelector</t>
   </si>
   <si>
+    <t>SkillSelector?</t>
+  </si>
+  <si>
     <t>array,SkillEffect</t>
   </si>
   <si>
+    <t>PassiveSkillTriggerType</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -296,6 +320,30 @@
     <t>参数2</t>
   </si>
   <si>
+    <t>子选择器（可空）</t>
+  </si>
+  <si>
+    <t>子选择器-目标阵营</t>
+  </si>
+  <si>
+    <t>子选择器-友方最大目标数，0=不限</t>
+  </si>
+  <si>
+    <t>子选择器-敌对最大目标数，0=不限</t>
+  </si>
+  <si>
+    <t>子选择器-是否包含施法者自身</t>
+  </si>
+  <si>
+    <t>子选择器-目标选取优先级</t>
+  </si>
+  <si>
+    <t>子选择器-参数1</t>
+  </si>
+  <si>
+    <t>子选择器-参数2</t>
+  </si>
+  <si>
     <t>伤害类型（仅用于展示，实际伤害类型由效果自身决定）</t>
   </si>
   <si>
@@ -314,6 +362,12 @@
     <t>技能效果1延迟触发</t>
   </si>
   <si>
+    <t>技能效果1作用范围</t>
+  </si>
+  <si>
+    <t>技能效果1生效血量阈值</t>
+  </si>
+  <si>
     <t>技能效果1参数1</t>
   </si>
   <si>
@@ -365,6 +419,12 @@
     <t>技能效果2延迟触发</t>
   </si>
   <si>
+    <t>技能效果2作用范围</t>
+  </si>
+  <si>
+    <t>技能效果2生效血量阈值</t>
+  </si>
+  <si>
     <t>技能效果2参数1</t>
   </si>
   <si>
@@ -404,6 +464,12 @@
     <t>技能效果3延迟触发</t>
   </si>
   <si>
+    <t>技能效果3作用范围</t>
+  </si>
+  <si>
+    <t>技能效果3生效血量阈值</t>
+  </si>
+  <si>
     <t>技能效果3参数1</t>
   </si>
   <si>
@@ -458,6 +524,21 @@
     <t>禁止冷却缩减</t>
   </si>
   <si>
+    <t>最大充能层数</t>
+  </si>
+  <si>
+    <t>单层充能恢复时间(毫秒)</t>
+  </si>
+  <si>
+    <t>引导时长(毫秒)</t>
+  </si>
+  <si>
+    <t>引导结算间隔(毫秒)</t>
+  </si>
+  <si>
+    <t>引导时移动是否中断</t>
+  </si>
+  <si>
     <t>受击硬直时间(毫秒)</t>
   </si>
   <si>
@@ -488,7 +569,7 @@
     <t>英雄技能</t>
   </si>
   <si>
-    <t>绿色</t>
+    <t>凡品</t>
   </si>
   <si>
     <t>|cff00FF00是所有剑术的基础，习得后获得大量准确，并提升极少量伤害。</t>
@@ -515,13 +596,13 @@
     <t>敌对</t>
   </si>
   <si>
+    <t>全部</t>
+  </si>
+  <si>
     <t>Attack One</t>
   </si>
   <si>
-    <t>ain_effect_jinengtexiao_01</t>
-  </si>
-  <si>
-    <t>Zs_Gongji1</t>
+    <t>无</t>
   </si>
   <si>
     <t>火球术</t>
@@ -530,7 +611,31 @@
     <t>Spell One</t>
   </si>
   <si>
-    <t>ani_effect_jinengtexiao_04</t>
+    <t>雷电术</t>
+  </si>
+  <si>
+    <t>圆月弯刀</t>
+  </si>
+  <si>
+    <t>奔雷术</t>
+  </si>
+  <si>
+    <t>烈火斩</t>
+  </si>
+  <si>
+    <t>万剑归元阵</t>
+  </si>
+  <si>
+    <t>四曜守元</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>焚天环剑诀</t>
   </si>
   <si>
     <t>icon_name</t>
@@ -930,9 +1035,6 @@
   </si>
   <si>
     <t>加施法状态</t>
-  </si>
-  <si>
-    <t>雷电术</t>
   </si>
   <si>
     <t>麻痹状态</t>
@@ -2333,8 +2435,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2345,6 +2446,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2787,2012 +2889,2476 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CT12"/>
+  <dimension ref="A1:DM13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="21"/>
-    <col min="2" max="2" width="10.3333333333333" style="21"/>
-    <col min="3" max="3" width="13.0833333333333" style="21" customWidth="1"/>
-    <col min="4" max="4" width="15.9166666666667" style="21" customWidth="1"/>
-    <col min="5" max="5" width="13.1666666666667" style="21" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="21" customWidth="1"/>
-    <col min="7" max="7" width="12.6666666666667" style="21" customWidth="1"/>
-    <col min="8" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="10.6666666666667" style="21" customWidth="1"/>
-    <col min="11" max="11" width="10.5833333333333" style="21" customWidth="1"/>
-    <col min="12" max="12" width="12" style="21" customWidth="1"/>
-    <col min="13" max="13" width="10.3333333333333" style="21"/>
-    <col min="14" max="14" width="14.8333333333333" style="21" customWidth="1"/>
-    <col min="15" max="15" width="10.3333333333333" style="21"/>
-    <col min="16" max="18" width="9" style="21"/>
-    <col min="19" max="19" width="11.6666666666667" style="21" customWidth="1"/>
-    <col min="20" max="21" width="9" style="21"/>
-    <col min="22" max="22" width="17.5833333333333" style="21" customWidth="1"/>
-    <col min="23" max="23" width="11.4166666666667" style="21" customWidth="1"/>
-    <col min="24" max="24" width="9.83333333333333" style="21" customWidth="1"/>
-    <col min="25" max="26" width="15.5" style="21" customWidth="1"/>
-    <col min="27" max="27" width="13.5833333333333" style="21" customWidth="1"/>
-    <col min="28" max="28" width="19.4166666666667" style="21" customWidth="1"/>
-    <col min="29" max="29" width="8.33333333333333" style="21" customWidth="1"/>
-    <col min="30" max="30" width="8.25" style="21" customWidth="1"/>
-    <col min="31" max="32" width="9" style="21"/>
-    <col min="33" max="33" width="19.1666666666667" style="21" customWidth="1"/>
-    <col min="34" max="34" width="23.4166666666667" style="21" customWidth="1"/>
-    <col min="35" max="35" width="19.1666666666667" style="21" customWidth="1"/>
-    <col min="36" max="36" width="9.25" style="21" customWidth="1"/>
-    <col min="37" max="83" width="16.0833333333333" style="21" customWidth="1"/>
-    <col min="84" max="85" width="9" style="21"/>
-    <col min="86" max="86" width="12.75" style="21" customWidth="1"/>
-    <col min="87" max="87" width="28.1" style="21" customWidth="1"/>
-    <col min="88" max="88" width="18.2" style="21" customWidth="1"/>
-    <col min="89" max="89" width="18.4" style="21" customWidth="1"/>
-    <col min="90" max="16384" width="9" style="21"/>
+    <col min="1" max="1" width="9" style="20" customWidth="1"/>
+    <col min="2" max="2" width="10.3333333333333" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.0833333333333" style="20" customWidth="1"/>
+    <col min="4" max="4" width="15.9166666666667" style="20" customWidth="1"/>
+    <col min="5" max="7" width="18.4" style="20" customWidth="1"/>
+    <col min="8" max="8" width="9" style="20" customWidth="1"/>
+    <col min="9" max="9" width="11.8" style="20" customWidth="1"/>
+    <col min="10" max="10" width="10.6666666666667" style="20" customWidth="1"/>
+    <col min="11" max="11" width="12.8" style="20" customWidth="1"/>
+    <col min="12" max="12" width="12" style="20" customWidth="1"/>
+    <col min="13" max="13" width="10.3333333333333" style="20" customWidth="1"/>
+    <col min="14" max="14" width="14.9" style="20" customWidth="1"/>
+    <col min="15" max="15" width="11.8" style="20" customWidth="1"/>
+    <col min="16" max="18" width="9" style="20" customWidth="1"/>
+    <col min="19" max="19" width="11.6666666666667" style="20" customWidth="1"/>
+    <col min="20" max="20" width="9" style="20" customWidth="1"/>
+    <col min="21" max="21" width="18.4" style="20" customWidth="1"/>
+    <col min="22" max="22" width="17.5833333333333" style="20" customWidth="1"/>
+    <col min="23" max="23" width="11.4166666666667" style="20" customWidth="1"/>
+    <col min="24" max="24" width="9.83333333333333" style="20" customWidth="1"/>
+    <col min="25" max="26" width="15.5" style="20" customWidth="1"/>
+    <col min="27" max="27" width="13.5833333333333" style="20" customWidth="1"/>
+    <col min="28" max="28" width="25.1" style="20" customWidth="1"/>
+    <col min="29" max="29" width="8.33333333333333" style="20" customWidth="1"/>
+    <col min="30" max="30" width="8.25" style="20" customWidth="1"/>
+    <col min="31" max="31" width="9" style="20" customWidth="1"/>
+    <col min="32" max="32" width="19.4" style="20" customWidth="1"/>
+    <col min="33" max="34" width="35.8" style="20" customWidth="1"/>
+    <col min="35" max="35" width="30.5" style="20" customWidth="1"/>
+    <col min="36" max="36" width="9.25" style="20" customWidth="1"/>
+    <col min="37" max="40" width="16.0833333333333" style="20" customWidth="1"/>
+    <col min="41" max="41" width="19.7" style="20" customWidth="1"/>
+    <col min="42" max="42" width="24.2" style="20" customWidth="1"/>
+    <col min="43" max="44" width="19.7" style="20" customWidth="1"/>
+    <col min="45" max="83" width="16.0833333333333" style="20" customWidth="1"/>
+    <col min="84" max="85" width="9" style="20" customWidth="1"/>
+    <col min="86" max="86" width="12.75" style="20" customWidth="1"/>
+    <col min="87" max="87" width="28.0833333333333" style="20" customWidth="1"/>
+    <col min="88" max="88" width="18.1666666666667" style="20" customWidth="1"/>
+    <col min="89" max="89" width="18.4166666666667" style="20" customWidth="1"/>
+    <col min="90" max="90" width="9" style="20" customWidth="1"/>
+    <col min="91" max="99" width="9" style="20"/>
+    <col min="100" max="100" width="13.9" style="20" customWidth="1"/>
+    <col min="101" max="101" width="28.1" style="20" customWidth="1"/>
+    <col min="102" max="102" width="18.2" style="20" customWidth="1"/>
+    <col min="103" max="103" width="18.4" style="20" customWidth="1"/>
+    <col min="104" max="104" width="13.9" style="20" customWidth="1"/>
+    <col min="105" max="109" width="9" style="20"/>
+    <col min="110" max="110" width="19.9" style="20" customWidth="1"/>
+    <col min="111" max="111" width="23.3" style="20" customWidth="1"/>
+    <col min="112" max="112" width="9" style="20"/>
+    <col min="113" max="114" width="16.2" style="20" customWidth="1"/>
+    <col min="115" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:117">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="Q1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="S1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="21" t="s">
+      <c r="T1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="21" t="s">
+      <c r="U1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="21" t="s">
+      <c r="V1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="W1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="21" t="s">
+      <c r="AE1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="21" t="s">
+      <c r="AM1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="23" t="s">
+      <c r="AN1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="23"/>
-      <c r="AR1" s="23"/>
+      <c r="AO1" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="AS1" s="23"/>
       <c r="AT1" s="23"/>
-      <c r="AU1" s="23"/>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23"/>
-      <c r="AX1" s="23"/>
-      <c r="AY1" s="23"/>
-      <c r="AZ1" s="23"/>
-      <c r="BA1" s="23"/>
-      <c r="BB1" s="23"/>
-      <c r="BC1" s="23"/>
-      <c r="BD1" s="23"/>
-      <c r="BE1" s="23"/>
-      <c r="BF1" s="23"/>
-      <c r="BG1" s="23"/>
-      <c r="BH1" s="23"/>
-      <c r="BI1" s="23"/>
-      <c r="BJ1" s="23"/>
-      <c r="BK1" s="23"/>
       <c r="BL1" s="23"/>
       <c r="BM1" s="23"/>
-      <c r="BN1" s="23"/>
-      <c r="BO1" s="23"/>
-      <c r="BP1" s="23"/>
-      <c r="BQ1" s="23"/>
-      <c r="BR1" s="23"/>
-      <c r="BS1" s="23"/>
-      <c r="BT1" s="23"/>
-      <c r="BU1" s="23"/>
-      <c r="BV1" s="23"/>
-      <c r="BW1" s="23"/>
-      <c r="BX1" s="23"/>
-      <c r="BY1" s="23"/>
-      <c r="BZ1" s="23"/>
-      <c r="CA1" s="23"/>
-      <c r="CB1" s="23"/>
-      <c r="CC1" s="23"/>
-      <c r="CD1" s="23"/>
       <c r="CE1" s="23"/>
-      <c r="CF1" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="CG1" s="21" t="s">
+      <c r="CF1" s="23"/>
+      <c r="CT1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="CH1" s="21" t="s">
+      <c r="CU1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="CI1" s="21" t="s">
+      <c r="CV1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="CJ1" s="21" t="s">
+      <c r="CW1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="CK1" s="21" t="s">
+      <c r="CX1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="CL1" s="21" t="s">
+      <c r="CY1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="CM1" s="21" t="s">
+      <c r="CZ1" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="CN1" s="21" t="s">
+      <c r="DA1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="CO1" s="21" t="s">
+      <c r="DB1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="CP1" s="21" t="s">
+      <c r="DC1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="CQ1" s="21" t="s">
+      <c r="DD1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="CR1" s="21" t="s">
+      <c r="DE1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="CS1" s="21" t="s">
+      <c r="DF1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="CT1" s="21" t="s">
+      <c r="DG1" s="20" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:98">
-      <c r="A2" s="21" t="s">
+      <c r="DH1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="DI1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="DJ1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="21" t="s">
+      <c r="DK1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="DL1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="21" t="s">
+      <c r="DM1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="21" t="s">
+    </row>
+    <row r="2" spans="1:117">
+      <c r="A2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="W2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG2" s="23" t="s">
+      <c r="D2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="23"/>
+      <c r="F2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO2" s="22" t="s">
+        <v>57</v>
+      </c>
       <c r="AS2" s="23"/>
       <c r="AT2" s="23"/>
-      <c r="AU2" s="23"/>
-      <c r="AV2" s="23"/>
-      <c r="AW2" s="23"/>
-      <c r="AX2" s="23"/>
-      <c r="AY2" s="23"/>
-      <c r="AZ2" s="23"/>
-      <c r="BA2" s="23"/>
-      <c r="BB2" s="23"/>
-      <c r="BC2" s="23"/>
-      <c r="BD2" s="23"/>
-      <c r="BE2" s="23"/>
-      <c r="BF2" s="23"/>
-      <c r="BG2" s="23"/>
-      <c r="BH2" s="23"/>
-      <c r="BI2" s="23"/>
-      <c r="BJ2" s="23"/>
-      <c r="BK2" s="23"/>
       <c r="BL2" s="23"/>
       <c r="BM2" s="23"/>
-      <c r="BN2" s="23"/>
-      <c r="BO2" s="23"/>
-      <c r="BP2" s="23"/>
-      <c r="BQ2" s="23"/>
-      <c r="BR2" s="23"/>
-      <c r="BS2" s="23"/>
-      <c r="BT2" s="23"/>
-      <c r="BU2" s="23"/>
-      <c r="BV2" s="23"/>
-      <c r="BW2" s="23"/>
-      <c r="BX2" s="23"/>
-      <c r="BY2" s="23"/>
-      <c r="BZ2" s="23"/>
-      <c r="CA2" s="23"/>
-      <c r="CB2" s="23"/>
-      <c r="CC2" s="23"/>
-      <c r="CD2" s="23"/>
       <c r="CE2" s="23"/>
-      <c r="CF2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="CG2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="CH2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CI2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CJ2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CK2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CL2" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="CM2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="CN2" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="CO2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="CP2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CQ2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CR2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="CS2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="CT2" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:98">
-      <c r="A3" s="21" t="s">
+      <c r="CF2" s="23"/>
+      <c r="CT2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="CU2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="CV2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="CW2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="CX2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="CY2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="CZ2" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="W3" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
+      <c r="DA2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DB2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="DC2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DD2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DE2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DF2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DG2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="DH2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DI2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DJ2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="DK2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="DL2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="DM2" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:117">
+      <c r="A3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO3" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="AS3" s="23"/>
       <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="23"/>
-      <c r="AZ3" s="23"/>
-      <c r="BA3" s="23"/>
-      <c r="BB3" s="23"/>
-      <c r="BC3" s="23"/>
-      <c r="BD3" s="23"/>
-      <c r="BE3" s="23"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="23"/>
-      <c r="BH3" s="23"/>
-      <c r="BI3" s="23"/>
-      <c r="BJ3" s="23"/>
-      <c r="BK3" s="23"/>
       <c r="BL3" s="23"/>
       <c r="BM3" s="23"/>
-      <c r="BN3" s="23"/>
-      <c r="BO3" s="23"/>
-      <c r="BP3" s="23"/>
-      <c r="BQ3" s="23"/>
-      <c r="BR3" s="23"/>
-      <c r="BS3" s="23"/>
-      <c r="BT3" s="23"/>
-      <c r="BU3" s="23"/>
-      <c r="BV3" s="23"/>
-      <c r="BW3" s="23"/>
-      <c r="BX3" s="23"/>
-      <c r="BY3" s="23"/>
-      <c r="BZ3" s="23"/>
-      <c r="CA3" s="23"/>
-      <c r="CB3" s="23"/>
-      <c r="CC3" s="23"/>
-      <c r="CD3" s="23"/>
       <c r="CE3" s="23"/>
-      <c r="CF3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CG3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CH3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CI3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CJ3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CK3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CL3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CM3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CN3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CO3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CP3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CQ3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CR3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CS3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="CT3" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:98">
-      <c r="A4" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="21" t="s">
+      <c r="CF3" s="23"/>
+      <c r="CT3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="CU3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="CV3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="CW3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="CX3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="CY3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="CZ3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DA3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DB3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DC3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DD3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DE3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DF3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DG3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DH3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DI3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DJ3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DK3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DL3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="DM3" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:117">
+      <c r="A4" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="H4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="21" t="s">
+      <c r="I4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="J4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="K4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="T4" s="21" t="s">
+      <c r="L4" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="U4" s="21" t="s">
+      <c r="M4" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="V4" s="21" t="s">
+      <c r="N4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="W4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="X4" s="21" t="s">
+      <c r="P4" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="Y4" s="21" t="s">
+      <c r="Q4" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="R4" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="S4" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="AB4" s="21" t="s">
+      <c r="T4" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="AC4" s="21" t="s">
+      <c r="U4" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="21" t="s">
+      <c r="V4" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AE4" s="21" t="s">
+      <c r="W4" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="AF4" s="21" t="s">
+      <c r="X4" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="AG4" s="21" t="s">
+      <c r="Y4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AH4" s="21" t="s">
+      <c r="Z4" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="AI4" s="21" t="s">
+      <c r="AA4" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="AJ4" s="21" t="s">
+      <c r="AB4" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="AK4" s="21" t="s">
+      <c r="AC4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="AL4" s="21" t="s">
+      <c r="AD4" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="AM4" s="21" t="s">
+      <c r="AE4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AN4" s="21" t="s">
+      <c r="AF4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="AO4" s="21" t="s">
+      <c r="AG4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="AP4" s="21" t="s">
+      <c r="AH4" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AQ4" s="21" t="s">
+      <c r="AI4" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AR4" s="21" t="s">
+      <c r="AJ4" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AS4" s="21" t="s">
+      <c r="AK4" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AT4" s="21" t="s">
+      <c r="AL4" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AU4" s="21" t="s">
+      <c r="AM4" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="AV4" s="21" t="s">
+      <c r="AN4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="AW4" s="21" t="s">
+      <c r="AO4" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="AX4" s="21" t="s">
+      <c r="AP4" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="AY4" s="21" t="s">
+      <c r="AQ4" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="AZ4" s="21" t="s">
+      <c r="AR4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="BA4" s="21" t="s">
+      <c r="AS4" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="BB4" s="21" t="s">
+      <c r="AT4" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="BC4" s="21" t="s">
+      <c r="AU4" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="BD4" s="21" t="s">
+      <c r="AV4" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="BE4" s="21" t="s">
+      <c r="AW4" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="BF4" s="21" t="s">
+      <c r="AX4" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="BG4" s="21" t="s">
+      <c r="AY4" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="BH4" s="21" t="s">
+      <c r="AZ4" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="BI4" s="21" t="s">
+      <c r="BA4" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="BJ4" s="21" t="s">
+      <c r="BB4" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BK4" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL4" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="BM4" s="21" t="s">
+      <c r="BC4" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="BD4" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE4" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF4" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="BH4" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="BI4" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BJ4" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="BK4" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL4" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="BM4" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO4" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="BP4" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ4" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR4" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS4" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU4" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV4" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW4" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX4" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="BY4" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="CA4" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CB4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CC4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="CD4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="CE4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="CF4" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="CG4" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="CH4" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="CI4" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="CJ4" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="CK4" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="CL4" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="CM4" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="CN4" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="CO4" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="CP4" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="CQ4" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="CR4" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="CS4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT4" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="CU4" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="CV4" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="CW4" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="CX4" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="CY4" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="CZ4" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="DA4" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="DB4" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC4" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="DD4" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="DE4" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="DF4" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="DG4" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="DH4" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="DI4" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="DJ4" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="DK4" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="DL4" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="DM4" s="20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:117">
+      <c r="B5" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O5" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P5" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>0</v>
+      </c>
+      <c r="R5" s="20">
+        <v>1</v>
+      </c>
+      <c r="S5" s="20">
         <v>100</v>
       </c>
-      <c r="BN4" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="BO4" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP4" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="BQ4" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR4" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS4" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT4" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU4" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV4" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW4" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX4" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY4" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ4" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="CA4" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB4" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="CC4" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="CD4" s="21" t="s">
+      <c r="T5" s="20">
+        <v>150</v>
+      </c>
+      <c r="U5" s="20">
+        <v>150</v>
+      </c>
+      <c r="V5" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X5" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="23"/>
+      <c r="AK5" s="23"/>
+      <c r="AL5" s="23"/>
+      <c r="AM5" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN5" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AO5" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP5" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ5" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW5" s="20">
+        <v>3</v>
+      </c>
+      <c r="AX5" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>10000</v>
+      </c>
+      <c r="BL5" s="23"/>
+      <c r="BM5" s="23"/>
+      <c r="CE5" s="23"/>
+      <c r="CF5" s="23"/>
+      <c r="CT5" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU5" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV5" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="CW5" s="20">
+        <v>30001</v>
+      </c>
+      <c r="CZ5" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG5" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI5" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL5" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM5" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:117">
+      <c r="B6" s="20">
+        <v>10010002</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O6" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="20">
+        <v>7</v>
+      </c>
+      <c r="S6" s="20">
         <v>100</v>
       </c>
-      <c r="CE4" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="CF4" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG4" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CH4" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI4" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="CJ4" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CK4" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CL4" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="CM4" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CN4" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="CO4" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="CP4" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="CQ4" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="CR4" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="CS4" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="CT4" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:98">
-      <c r="B5" s="21">
+      <c r="T6" s="20">
+        <v>150</v>
+      </c>
+      <c r="U6" s="20">
+        <v>150</v>
+      </c>
+      <c r="V6" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W6" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X6" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="23"/>
+      <c r="AJ6" s="23"/>
+      <c r="AK6" s="23"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN6" s="20">
+        <v>10400</v>
+      </c>
+      <c r="AO6" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP6" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ6" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW6" s="20">
+        <v>4</v>
+      </c>
+      <c r="AX6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>10000</v>
+      </c>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="23"/>
+      <c r="CE6" s="23"/>
+      <c r="CF6" s="23"/>
+      <c r="CT6" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU6" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV6" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW6" s="20">
+        <v>30002</v>
+      </c>
+      <c r="CZ6" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI6" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL6" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM6" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:117">
+      <c r="B7" s="20">
+        <v>10010003</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
+        <v>1</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O7" s="20">
         <v>10010001</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="21">
-        <v>0</v>
-      </c>
-      <c r="H5" s="21">
+      <c r="P7" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>2</v>
+      </c>
+      <c r="R7" s="20">
+        <v>11</v>
+      </c>
+      <c r="S7" s="20">
+        <v>100</v>
+      </c>
+      <c r="T7" s="20">
+        <v>150</v>
+      </c>
+      <c r="U7" s="20">
+        <v>150</v>
+      </c>
+      <c r="V7" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W7" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X7" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y7" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="20">
         <v>1</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L5" s="21">
-        <v>10010002</v>
-      </c>
-      <c r="N5" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O5" s="21">
+      <c r="AA7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="23"/>
+      <c r="AG7" s="23"/>
+      <c r="AH7" s="23"/>
+      <c r="AI7" s="23"/>
+      <c r="AJ7" s="23"/>
+      <c r="AK7" s="23"/>
+      <c r="AL7" s="23"/>
+      <c r="AM7" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN7" s="20">
+        <v>10800</v>
+      </c>
+      <c r="AO7" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP7" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ7" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW7" s="20">
+        <v>5</v>
+      </c>
+      <c r="AX7" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>10000</v>
+      </c>
+      <c r="BL7" s="23"/>
+      <c r="BM7" s="23"/>
+      <c r="CE7" s="23"/>
+      <c r="CF7" s="23"/>
+      <c r="CT7" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU7" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV7" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW7" s="20">
+        <v>30003</v>
+      </c>
+      <c r="CZ7" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG7" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI7" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL7" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM7" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:117">
+      <c r="B8" s="20">
+        <v>10010004</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <v>1</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O8" s="20">
         <v>10010001</v>
       </c>
-      <c r="P5" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>0</v>
-      </c>
-      <c r="R5" s="21">
+      <c r="P8" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>3</v>
+      </c>
+      <c r="R8" s="20">
+        <v>16</v>
+      </c>
+      <c r="S8" s="20">
+        <v>100</v>
+      </c>
+      <c r="T8" s="20">
+        <v>150</v>
+      </c>
+      <c r="U8" s="20">
+        <v>150</v>
+      </c>
+      <c r="V8" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W8" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X8" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y8" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="20">
         <v>1</v>
       </c>
-      <c r="S5" s="21">
+      <c r="AA8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="23"/>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="23"/>
+      <c r="AK8" s="23"/>
+      <c r="AL8" s="23"/>
+      <c r="AM8" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN8" s="20">
+        <v>11200</v>
+      </c>
+      <c r="AO8" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP8" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ8" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW8" s="20">
+        <v>6</v>
+      </c>
+      <c r="AX8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>10000</v>
+      </c>
+      <c r="BL8" s="23"/>
+      <c r="BM8" s="23"/>
+      <c r="CE8" s="23"/>
+      <c r="CF8" s="23"/>
+      <c r="CT8" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU8" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV8" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="CW8" s="20">
+        <v>30004</v>
+      </c>
+      <c r="CZ8" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI8" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK8" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL8" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM8" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:117">
+      <c r="B9" s="20">
+        <v>10010005</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20">
+        <v>1</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O9" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>3</v>
+      </c>
+      <c r="R9" s="20">
+        <v>25</v>
+      </c>
+      <c r="S9" s="20">
         <v>100</v>
       </c>
-      <c r="T5" s="21">
+      <c r="T9" s="20">
         <v>150</v>
       </c>
-      <c r="U5" s="21">
+      <c r="U9" s="20">
         <v>150</v>
       </c>
-      <c r="V5" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W5" s="21" t="s">
+      <c r="V9" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W9" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X9" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y9" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="20">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="23"/>
+      <c r="AJ9" s="23"/>
+      <c r="AK9" s="23"/>
+      <c r="AL9" s="23"/>
+      <c r="AM9" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN9" s="20">
+        <v>11300</v>
+      </c>
+      <c r="AO9" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP9" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ9" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW9" s="20">
+        <v>6</v>
+      </c>
+      <c r="AX9" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>10000</v>
+      </c>
+      <c r="BL9" s="23"/>
+      <c r="BM9" s="23"/>
+      <c r="CE9" s="23"/>
+      <c r="CF9" s="23"/>
+      <c r="CT9" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU9" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV9" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW9" s="20">
+        <v>30005</v>
+      </c>
+      <c r="CZ9" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG9" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI9" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK9" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL9" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM9" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:117">
+      <c r="B10" s="20">
+        <v>10010006</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="20">
+        <v>0</v>
+      </c>
+      <c r="H10" s="20">
+        <v>1</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O10" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P10" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>3</v>
+      </c>
+      <c r="R10" s="20">
+        <v>30</v>
+      </c>
+      <c r="S10" s="20">
+        <v>100</v>
+      </c>
+      <c r="T10" s="20">
         <v>150</v>
       </c>
-      <c r="X5" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y5" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="21">
+      <c r="U10" s="20">
+        <v>150</v>
+      </c>
+      <c r="V10" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W10" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X10" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y10" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="20">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="23"/>
+      <c r="AF10" s="23"/>
+      <c r="AG10" s="23"/>
+      <c r="AH10" s="23"/>
+      <c r="AI10" s="23"/>
+      <c r="AJ10" s="23"/>
+      <c r="AK10" s="23"/>
+      <c r="AL10" s="23"/>
+      <c r="AM10" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN10" s="20">
+        <v>11600</v>
+      </c>
+      <c r="AO10" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP10" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ10" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW10" s="20">
+        <v>7</v>
+      </c>
+      <c r="AX10" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>10000</v>
+      </c>
+      <c r="BL10" s="23"/>
+      <c r="BM10" s="23"/>
+      <c r="CE10" s="23"/>
+      <c r="CF10" s="23"/>
+      <c r="CT10" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU10" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV10" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="CW10" s="20">
+        <v>30006</v>
+      </c>
+      <c r="CZ10" s="20">
         <v>1</v>
       </c>
-      <c r="AA5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF5" s="21">
+      <c r="DB10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG10" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI10" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK10" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL10" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM10" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:117">
+      <c r="B11" s="20">
+        <v>10010007</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O11" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>3</v>
+      </c>
+      <c r="R11" s="20">
+        <v>35</v>
+      </c>
+      <c r="S11" s="20">
+        <v>100</v>
+      </c>
+      <c r="T11" s="20">
+        <v>150</v>
+      </c>
+      <c r="U11" s="20">
+        <v>150</v>
+      </c>
+      <c r="V11" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W11" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X11" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="20">
+        <v>20</v>
+      </c>
+      <c r="AA11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="23"/>
+      <c r="AF11" s="23"/>
+      <c r="AG11" s="23"/>
+      <c r="AH11" s="23"/>
+      <c r="AI11" s="23"/>
+      <c r="AJ11" s="23"/>
+      <c r="AK11" s="23"/>
+      <c r="AL11" s="23"/>
+      <c r="AM11" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN11" s="20">
+        <v>11700</v>
+      </c>
+      <c r="AO11" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP11" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ11" s="20">
         <v>10000</v>
       </c>
-      <c r="AG5" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI5" s="21">
+      <c r="AR11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="20">
         <v>10000</v>
       </c>
-      <c r="AJ5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL5" s="21">
+      <c r="AW11" s="20">
+        <v>7</v>
+      </c>
+      <c r="AX11" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
         <v>10000</v>
       </c>
-      <c r="AM5" s="21">
+      <c r="BL11" s="23"/>
+      <c r="BM11" s="23"/>
+      <c r="CE11" s="23"/>
+      <c r="CF11" s="23"/>
+      <c r="CT11" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU11" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV11" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW11" s="20">
+        <v>30007</v>
+      </c>
+      <c r="CZ11" s="20">
+        <v>1</v>
+      </c>
+      <c r="DB11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG11" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI11" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK11" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL11" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM11" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:117">
+      <c r="B12" s="20">
+        <v>10010008</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0</v>
+      </c>
+      <c r="H12" s="20">
+        <v>1</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O12" s="20">
+        <v>10010001</v>
+      </c>
+      <c r="P12" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="20">
         <v>3</v>
       </c>
-      <c r="AN5" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF5" s="21">
+      <c r="R12" s="20">
+        <v>35</v>
+      </c>
+      <c r="S12" s="20">
+        <v>100</v>
+      </c>
+      <c r="T12" s="20">
+        <v>0</v>
+      </c>
+      <c r="U12" s="20">
+        <v>0</v>
+      </c>
+      <c r="V12" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X12" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y12" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="23"/>
+      <c r="AI12" s="23"/>
+      <c r="AJ12" s="23"/>
+      <c r="AK12" s="23"/>
+      <c r="AL12" s="23"/>
+      <c r="AM12" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="AN12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP12" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="AQ12" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW12" s="20">
+        <v>7</v>
+      </c>
+      <c r="AX12" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>10000</v>
+      </c>
+      <c r="BL12" s="23"/>
+      <c r="BM12" s="23"/>
+      <c r="CE12" s="23"/>
+      <c r="CF12" s="23"/>
+      <c r="CT12" s="20">
         <v>10</v>
       </c>
-      <c r="CG5" s="21">
+      <c r="CU12" s="20">
         <v>20</v>
       </c>
-      <c r="CH5" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI5" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL5" s="21">
+      <c r="CV12" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW12" s="20">
+        <v>30008</v>
+      </c>
+      <c r="CZ12" s="20">
         <v>1</v>
       </c>
-      <c r="CN5" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP5" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS5" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT5" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:98">
-      <c r="B6" s="21">
-        <v>10010002</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>2</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L6" s="21">
-        <v>10010003</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O6" s="21">
+      <c r="DB12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG12" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI12" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK12" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL12" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM12" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:117">
+      <c r="B13" s="20">
+        <v>10010009</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>1</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O13" s="20">
         <v>10010001</v>
       </c>
-      <c r="P6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="21">
+      <c r="P13" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>3</v>
+      </c>
+      <c r="R13" s="20">
+        <v>40</v>
+      </c>
+      <c r="S13" s="20">
+        <v>100</v>
+      </c>
+      <c r="T13" s="20">
+        <v>0</v>
+      </c>
+      <c r="U13" s="20">
+        <v>0</v>
+      </c>
+      <c r="V13" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W13" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X13" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y13" s="20">
         <v>1</v>
       </c>
-      <c r="R6" s="21">
+      <c r="Z13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="23"/>
+      <c r="AH13" s="23"/>
+      <c r="AI13" s="23"/>
+      <c r="AJ13" s="23"/>
+      <c r="AK13" s="23"/>
+      <c r="AL13" s="23"/>
+      <c r="AM13" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="AN13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP13" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="AQ13" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AR13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="20">
+        <v>10000</v>
+      </c>
+      <c r="AW13" s="20">
         <v>7</v>
       </c>
-      <c r="S6" s="21">
-        <v>200</v>
-      </c>
-      <c r="T6" s="21">
-        <v>150</v>
-      </c>
-      <c r="U6" s="21">
-        <v>150</v>
-      </c>
-      <c r="V6" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W6" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X6" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="21">
+      <c r="AX13" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="20">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>10000</v>
+      </c>
+      <c r="BL13" s="23"/>
+      <c r="BM13" s="23"/>
+      <c r="CE13" s="23"/>
+      <c r="CF13" s="23"/>
+      <c r="CT13" s="20">
+        <v>10</v>
+      </c>
+      <c r="CU13" s="20">
+        <v>20</v>
+      </c>
+      <c r="CV13" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="CW13" s="20">
+        <v>30009</v>
+      </c>
+      <c r="CZ13" s="20">
         <v>1</v>
       </c>
-      <c r="AA6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF6" s="21">
-        <v>10400</v>
-      </c>
-      <c r="AG6" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH6" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI6" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL6" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM6" s="21">
-        <v>4</v>
-      </c>
-      <c r="AN6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF6" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG6" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH6" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="CI6" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="CL6" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN6" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP6" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS6" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT6" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:98">
-      <c r="B7" s="21">
-        <v>10010003</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-      <c r="H7" s="21">
-        <v>3</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L7" s="21">
-        <v>10010004</v>
-      </c>
-      <c r="M7" s="21">
-        <v>10010002</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O7" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="21">
-        <v>2</v>
-      </c>
-      <c r="R7" s="21">
-        <v>11</v>
-      </c>
-      <c r="S7" s="21">
-        <v>300</v>
-      </c>
-      <c r="T7" s="21">
-        <v>150</v>
-      </c>
-      <c r="U7" s="21">
-        <v>150</v>
-      </c>
-      <c r="V7" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W7" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X7" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF7" s="21">
-        <v>10800</v>
-      </c>
-      <c r="AG7" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH7" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI7" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL7" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM7" s="21">
-        <v>5</v>
-      </c>
-      <c r="AN7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF7" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG7" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH7" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI7" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL7" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN7" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP7" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS7" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT7" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:98">
-      <c r="B8" s="21">
-        <v>10010004</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>4</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L8" s="21">
-        <v>10010005</v>
-      </c>
-      <c r="M8" s="21">
-        <v>10010003</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O8" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>3</v>
-      </c>
-      <c r="R8" s="21">
-        <v>16</v>
-      </c>
-      <c r="T8" s="21">
-        <v>150</v>
-      </c>
-      <c r="U8" s="21">
-        <v>150</v>
-      </c>
-      <c r="V8" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W8" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X8" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF8" s="21">
-        <v>11200</v>
-      </c>
-      <c r="AG8" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH8" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI8" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL8" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM8" s="21">
-        <v>6</v>
-      </c>
-      <c r="AN8" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF8" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG8" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH8" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI8" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL8" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN8" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP8" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS8" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT8" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:98">
-      <c r="B9" s="21">
-        <v>10010005</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F9" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21">
-        <v>5</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L9" s="21">
-        <v>10010006</v>
-      </c>
-      <c r="M9" s="21">
-        <v>10010004</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O9" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>3</v>
-      </c>
-      <c r="R9" s="21">
-        <v>25</v>
-      </c>
-      <c r="T9" s="21">
-        <v>150</v>
-      </c>
-      <c r="U9" s="21">
-        <v>150</v>
-      </c>
-      <c r="V9" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W9" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X9" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF9" s="21">
-        <v>11300</v>
-      </c>
-      <c r="AG9" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH9" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI9" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL9" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM9" s="21">
-        <v>6</v>
-      </c>
-      <c r="AN9" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF9" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG9" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH9" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI9" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL9" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN9" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP9" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS9" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT9" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:98">
-      <c r="B10" s="21">
-        <v>10010006</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>6</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L10" s="21">
-        <v>10010007</v>
-      </c>
-      <c r="M10" s="21">
-        <v>10010005</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O10" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>3</v>
-      </c>
-      <c r="R10" s="21">
-        <v>30</v>
-      </c>
-      <c r="T10" s="21">
-        <v>150</v>
-      </c>
-      <c r="U10" s="21">
-        <v>150</v>
-      </c>
-      <c r="V10" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W10" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X10" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF10" s="21">
-        <v>11600</v>
-      </c>
-      <c r="AG10" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH10" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI10" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL10" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM10" s="21">
-        <v>7</v>
-      </c>
-      <c r="AN10" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF10" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG10" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH10" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI10" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL10" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN10" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP10" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS10" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT10" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:98">
-      <c r="B11" s="21">
-        <v>10010007</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F11" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0</v>
-      </c>
-      <c r="H11" s="21">
-        <v>7</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L11" s="21">
-        <v>10010008</v>
-      </c>
-      <c r="M11" s="21">
-        <v>10010006</v>
-      </c>
-      <c r="N11" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O11" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>3</v>
-      </c>
-      <c r="R11" s="21">
-        <v>35</v>
-      </c>
-      <c r="T11" s="21">
-        <v>150</v>
-      </c>
-      <c r="U11" s="21">
-        <v>150</v>
-      </c>
-      <c r="V11" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W11" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X11" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF11" s="21">
-        <v>11700</v>
-      </c>
-      <c r="AG11" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH11" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI11" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL11" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM11" s="21">
-        <v>7</v>
-      </c>
-      <c r="AN11" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF11" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG11" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH11" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI11" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL11" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP11" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS11" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT11" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:98">
-      <c r="B12" s="21">
-        <v>10010008</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0</v>
-      </c>
-      <c r="H12" s="21">
-        <v>8</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L12" s="21">
-        <v>10010009</v>
-      </c>
-      <c r="M12" s="21">
-        <v>10010007</v>
-      </c>
-      <c r="N12" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="O12" s="21">
-        <v>10010001</v>
-      </c>
-      <c r="P12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>3</v>
-      </c>
-      <c r="R12" s="21">
-        <v>40</v>
-      </c>
-      <c r="T12" s="21">
-        <v>150</v>
-      </c>
-      <c r="U12" s="21">
-        <v>150</v>
-      </c>
-      <c r="V12" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="W12" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="X12" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF12" s="21">
-        <v>11800</v>
-      </c>
-      <c r="AG12" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH12" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI12" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AJ12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL12" s="21">
-        <v>10000</v>
-      </c>
-      <c r="AM12" s="21">
-        <v>7</v>
-      </c>
-      <c r="AN12" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="21">
-        <v>0</v>
-      </c>
-      <c r="CF12" s="21">
-        <v>10</v>
-      </c>
-      <c r="CG12" s="21">
-        <v>20</v>
-      </c>
-      <c r="CH12" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="CI12" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="CL12" s="21">
-        <v>1</v>
-      </c>
-      <c r="CN12" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP12" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="CS12" s="21">
-        <v>0</v>
-      </c>
-      <c r="CT12" s="21">
+      <c r="DB13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DC13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DD13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DE13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DF13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DG13" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI13" s="20">
+        <v>10001</v>
+      </c>
+      <c r="DK13" t="s">
+        <v>185</v>
+      </c>
+      <c r="DL13" s="20">
+        <v>0</v>
+      </c>
+      <c r="DM13" s="20">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="W1:AD1"/>
-    <mergeCell ref="AG1:CE1"/>
+    <mergeCell ref="AE1:AL1"/>
+    <mergeCell ref="AO1:CS1"/>
     <mergeCell ref="W2:AD2"/>
-    <mergeCell ref="AG2:CE2"/>
+    <mergeCell ref="AE2:AL2"/>
+    <mergeCell ref="AO2:CS2"/>
     <mergeCell ref="W3:AD3"/>
-    <mergeCell ref="AG3:CE3"/>
+    <mergeCell ref="AE3:AL3"/>
+    <mergeCell ref="AO3:CS3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4806,6 +5372,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="5" max="5" width="10.0833333333333" customWidth="1"/>
+    <col min="17" max="17" width="29.5" customWidth="1"/>
     <col min="21" max="21" width="12.8333333333333" customWidth="1"/>
     <col min="22" max="23" width="13.4166666666667" customWidth="1"/>
     <col min="28" max="28" width="12.8333333333333" customWidth="1"/>
@@ -4822,16 +5389,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="F1" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="G1" t="s">
         <v>13</v>
@@ -4840,278 +5407,238 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="J1" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="K1" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="L1" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="M1" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="N1" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="O1" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="P1" t="s">
         <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="R1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S1" s="18" t="s">
-        <v>174</v>
+        <v>208</v>
+      </c>
+      <c r="S1" t="s">
+        <v>209</v>
       </c>
       <c r="T1" t="s">
-        <v>175</v>
-      </c>
-      <c r="U1" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
-      <c r="AM1" s="19"/>
-      <c r="AN1" s="19"/>
-      <c r="AO1" s="19"/>
+        <v>210</v>
+      </c>
+      <c r="U1" s="18" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>177</v>
+        <v>49</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>212</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>179</v>
+        <v>51</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>214</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>181</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>216</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="V2" s="19"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="F4" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="H4" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="I4" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="J4" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="K4" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="L4" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="M4" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="N4" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="O4" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="Q4" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="R4" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="S4" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="T4" t="s">
-        <v>201</v>
-      </c>
-      <c r="U4" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="V4" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="W4" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="X4" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y4" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z4" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA4" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB4" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC4" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD4" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG4" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="AH4" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI4" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="AJ4" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="AK4" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL4" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="AM4" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="AN4" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="AO4" s="18" t="s">
-        <v>222</v>
+        <v>236</v>
+      </c>
+      <c r="U4" t="s">
+        <v>237</v>
+      </c>
+      <c r="V4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W4" t="s">
+        <v>239</v>
+      </c>
+      <c r="X4" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>243</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>244</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>246</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>250</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>252</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>253</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>254</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>255</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>256</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -5119,28 +5646,28 @@
         <v>21000301</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>224</v>
+        <v>258</v>
+      </c>
+      <c r="E5" t="s">
+        <v>259</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="H5" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -5152,49 +5679,45 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U5" t="s">
-        <v>229</v>
-      </c>
-      <c r="V5" s="18">
+        <v>264</v>
+      </c>
+      <c r="V5">
         <v>10000</v>
       </c>
-      <c r="W5" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="18"/>
+      <c r="W5" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="6" spans="1:41">
       <c r="B6">
         <v>21000401</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="E6" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="H6" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -5206,49 +5729,45 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U6" t="s">
-        <v>229</v>
-      </c>
-      <c r="V6" s="18">
+        <v>264</v>
+      </c>
+      <c r="V6">
         <v>10000</v>
       </c>
-      <c r="W6" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="18"/>
-      <c r="AJ6" s="18"/>
-      <c r="AK6" s="18"/>
+      <c r="W6" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="7" spans="1:41">
       <c r="B7">
         <v>21000601</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="E7" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="H7" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -5257,49 +5776,45 @@
         <v>2000</v>
       </c>
       <c r="S7" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U7" t="s">
-        <v>229</v>
-      </c>
-      <c r="V7" s="18">
+        <v>264</v>
+      </c>
+      <c r="V7">
         <v>10000</v>
       </c>
-      <c r="W7" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="AC7" s="18"/>
-      <c r="AD7" s="18"/>
-      <c r="AJ7" s="18"/>
-      <c r="AK7" s="18"/>
+      <c r="W7" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="8" spans="1:41">
       <c r="B8">
         <v>21001001</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="D8" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -5311,50 +5826,48 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U8" t="s">
-        <v>239</v>
-      </c>
-      <c r="V8" s="18">
+        <v>274</v>
+      </c>
+      <c r="V8">
         <v>10000</v>
       </c>
       <c r="W8" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="X8">
         <v>-2000</v>
       </c>
-      <c r="AC8" s="18"/>
-      <c r="AJ8" s="18"/>
     </row>
     <row r="9" spans="1:41">
       <c r="B9">
         <v>21000201</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="H9" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -5366,22 +5879,22 @@
         <v>3000</v>
       </c>
       <c r="Q9" t="s">
-        <v>244</v>
-      </c>
-      <c r="R9" s="18" t="s">
-        <v>245</v>
+        <v>279</v>
+      </c>
+      <c r="R9" t="s">
+        <v>280</v>
       </c>
       <c r="S9" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U9" t="s">
-        <v>246</v>
-      </c>
-      <c r="V9" s="18">
+        <v>281</v>
+      </c>
+      <c r="V9">
         <v>10000</v>
       </c>
       <c r="W9" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="X9">
         <v>2200</v>
@@ -5395,36 +5908,34 @@
       <c r="AA9">
         <v>0</v>
       </c>
-      <c r="AC9" s="18"/>
-      <c r="AJ9" s="18"/>
     </row>
     <row r="10" spans="1:41">
       <c r="B10">
         <v>21000202</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="H10" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -5436,22 +5947,22 @@
         <v>3000</v>
       </c>
       <c r="Q10" t="s">
-        <v>244</v>
-      </c>
-      <c r="R10" s="18" t="s">
-        <v>245</v>
+        <v>279</v>
+      </c>
+      <c r="R10" t="s">
+        <v>280</v>
       </c>
       <c r="S10" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U10" t="s">
-        <v>246</v>
-      </c>
-      <c r="V10" s="18">
+        <v>281</v>
+      </c>
+      <c r="V10">
         <v>10000</v>
       </c>
       <c r="W10" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="X10">
         <v>2600</v>
@@ -5465,36 +5976,34 @@
       <c r="AA10">
         <v>0</v>
       </c>
-      <c r="AC10" s="18"/>
-      <c r="AJ10" s="18"/>
     </row>
     <row r="11" spans="1:41">
       <c r="B11">
         <v>21000203</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E11" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -5506,22 +6015,22 @@
         <v>3000</v>
       </c>
       <c r="Q11" t="s">
-        <v>244</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>245</v>
+        <v>279</v>
+      </c>
+      <c r="R11" t="s">
+        <v>280</v>
       </c>
       <c r="S11" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U11" t="s">
-        <v>246</v>
-      </c>
-      <c r="V11" s="18">
+        <v>281</v>
+      </c>
+      <c r="V11">
         <v>10000</v>
       </c>
       <c r="W11" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="X11">
         <v>3000</v>
@@ -5535,36 +6044,34 @@
       <c r="AA11">
         <v>0</v>
       </c>
-      <c r="AC11" s="18"/>
-      <c r="AJ11" s="18"/>
     </row>
     <row r="12" spans="1:41">
       <c r="B12">
         <v>21000204</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -5576,22 +6083,22 @@
         <v>3000</v>
       </c>
       <c r="Q12" t="s">
-        <v>244</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>245</v>
+        <v>279</v>
+      </c>
+      <c r="R12" t="s">
+        <v>280</v>
       </c>
       <c r="S12" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="U12" t="s">
-        <v>246</v>
-      </c>
-      <c r="V12" s="18">
+        <v>281</v>
+      </c>
+      <c r="V12">
         <v>10000</v>
       </c>
       <c r="W12" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="X12">
         <v>3600</v>
@@ -5605,8 +6112,6 @@
       <c r="AA12">
         <v>0</v>
       </c>
-      <c r="AC12" s="18"/>
-      <c r="AJ12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5631,33 +6136,33 @@
     <col min="5" max="5" width="23.3333333333333" style="17" customWidth="1"/>
     <col min="6" max="6" width="4.58333333333333" style="17" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="16" customWidth="1"/>
-    <col min="8" max="8" width="8.25" style="16" customWidth="1"/>
-    <col min="9" max="16384" width="8.25" style="16"/>
+    <col min="8" max="9" width="8.25" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="8.25" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="16" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B2" s="16">
         <v>1</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="F2" s="17">
         <v>1</v>
@@ -5665,13 +6170,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="B3" s="16">
         <v>2</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="F3" s="17">
         <v>2</v>
@@ -5679,13 +6184,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="16" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="B4" s="16">
         <v>3</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="F4" s="17">
         <v>3</v>
@@ -5693,13 +6198,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="B5" s="16">
         <v>4</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="F5" s="17">
         <v>4</v>
@@ -5707,13 +6212,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="B6" s="16">
         <v>5</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="F6" s="17">
         <v>5</v>
@@ -5721,13 +6226,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="B7" s="16">
         <v>6</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="F7" s="17">
         <v>6</v>
@@ -5735,13 +6240,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="B8" s="16">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="F8" s="17">
         <v>7</v>
@@ -5749,13 +6254,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="16" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B9" s="16">
         <v>8</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="F9" s="17">
         <v>8</v>
@@ -5763,13 +6268,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="16" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="B10" s="16">
         <v>9</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="F10" s="17">
         <v>9</v>
@@ -5777,13 +6282,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="16" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B11" s="16">
         <v>10</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="F11" s="17">
         <v>10</v>
@@ -5791,13 +6296,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="16" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="B12" s="16">
         <v>11</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="F12" s="17">
         <v>11</v>
@@ -5805,13 +6310,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="16" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B13" s="16">
         <v>12</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="F13" s="17">
         <v>12</v>
@@ -5819,13 +6324,13 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="16" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="B14" s="16">
         <v>13</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="F14" s="17">
         <v>13</v>
@@ -5833,13 +6338,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="16" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="B15" s="16">
         <v>14</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="F15" s="17">
         <v>14</v>
@@ -5847,13 +6352,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="16" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="B16" s="16">
         <v>15</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="F16" s="17">
         <v>15</v>
@@ -5861,13 +6366,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="16" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="B17" s="16">
         <v>16</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="F17" s="17">
         <v>16</v>
@@ -5875,13 +6380,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="16" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B18" s="16">
         <v>17</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="F18" s="17">
         <v>17</v>
@@ -5889,13 +6394,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="16" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="B19" s="16">
         <v>18</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="F19" s="17">
         <v>18</v>
@@ -5906,7 +6411,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="F20" s="17">
         <v>19</v>
@@ -5917,7 +6422,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="F21" s="17">
         <v>20</v>
@@ -5928,7 +6433,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="F22" s="17">
         <v>21</v>
@@ -5939,7 +6444,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="F23" s="17">
         <v>22</v>
@@ -5950,7 +6455,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="F24" s="17">
         <v>23</v>
@@ -5961,7 +6466,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="F25" s="17">
         <v>24</v>
@@ -5972,7 +6477,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="F26" s="17">
         <v>25</v>
@@ -5983,7 +6488,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="F27" s="17">
         <v>26</v>
@@ -5994,7 +6499,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="F28" s="17">
         <v>27</v>
@@ -6005,7 +6510,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="F29" s="17">
         <v>28</v>
@@ -6016,7 +6521,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="F30" s="17">
         <v>29</v>
@@ -6027,7 +6532,7 @@
         <v>30</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="F31" s="17">
         <v>30</v>
@@ -6035,13 +6540,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="16" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="B32" s="16">
         <v>31</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="F32" s="17">
         <v>31</v>
@@ -6049,13 +6554,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="16" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="B33" s="16">
         <v>32</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="F33" s="17">
         <v>32</v>
@@ -6063,13 +6568,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="16" t="s">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="B34" s="16">
         <v>33</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="F34" s="17">
         <v>33</v>
@@ -6077,7 +6582,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="16" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="B35" s="16">
         <v>34</v>
@@ -6088,13 +6593,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="16" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="B36" s="16">
         <v>35</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="F36" s="17">
         <v>35</v>
@@ -6102,13 +6607,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="16" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="B37" s="16">
         <v>36</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="F37" s="17">
         <v>36</v>
@@ -6116,13 +6621,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="16" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B38" s="16">
         <v>37</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="F38" s="17">
         <v>37</v>
@@ -6158,7 +6663,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="16" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B44" s="16">
         <v>43</v>
@@ -6166,7 +6671,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="16" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="B45" s="16">
         <v>44</v>
@@ -6254,7 +6759,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="16" t="s">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="B62" s="16">
         <v>61</v>
@@ -6262,7 +6767,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="16" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="B63" s="16">
         <v>62</v>
@@ -6270,7 +6775,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="16" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="B64" s="16">
         <v>63</v>
@@ -6278,7 +6783,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="16" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="B65" s="16">
         <v>64</v>
@@ -6286,7 +6791,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="16" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="B66" s="16">
         <v>65</v>
@@ -6294,7 +6799,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="16" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B67" s="16">
         <v>66</v>
@@ -6302,7 +6807,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="16" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="B68" s="16">
         <v>67</v>
@@ -6310,7 +6815,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="16" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="B69" s="16">
         <v>68</v>
@@ -6478,7 +6983,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="16" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="B102" s="16">
         <v>101</v>
@@ -6486,7 +6991,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="16" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="B103" s="16">
         <v>102</v>
@@ -6494,7 +6999,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="16" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="B104" s="16">
         <v>103</v>
@@ -6502,7 +7007,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="16" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="B105" s="16">
         <v>104</v>
@@ -6510,7 +7015,7 @@
     </row>
     <row r="106" ht="16.5" customHeight="1" spans="1:2">
       <c r="A106" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="B106" s="16">
         <v>105</v>
@@ -6518,7 +7023,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="16" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="B107" s="16">
         <v>106</v>
@@ -6590,592 +7095,592 @@
     <col min="16" max="16" width="10.8333333333333" style="1" customWidth="1"/>
     <col min="17" max="17" width="1.83333333333333" style="1" customWidth="1"/>
     <col min="18" max="18" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.25" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.25" style="1"/>
+    <col min="19" max="20" width="8.25" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.25" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:15">
       <c r="A1" s="3" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:15">
       <c r="A2" s="6" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="6" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="4" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="6" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="8" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="7" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="F8" s="9" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="11" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="F9" s="9" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="11" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="F10" s="9" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="11" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="F11" s="9" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="11" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="F12" s="12" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="11" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="F13" s="6"/>
       <c r="H13" s="11" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="F14" s="6"/>
       <c r="H14" s="11" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="F15" s="6"/>
       <c r="H15" s="11" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="K15" s="1"/>
       <c r="M15" s="7" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="F16" s="6"/>
       <c r="H16" s="11" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="F17" s="6"/>
       <c r="H17" s="11" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="K17" s="1"/>
       <c r="M17" s="7" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="F18" s="6"/>
       <c r="I18" s="1" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="K18" s="1"/>
       <c r="M18" s="7" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="F19" s="6"/>
       <c r="K19" s="1"/>
       <c r="M19" s="7" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="F20" s="6"/>
       <c r="K20" s="1"/>
       <c r="M20" s="7" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="3" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="F21" s="6"/>
       <c r="K21" s="1"/>
       <c r="M21" s="7" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="G22" s="6"/>
       <c r="K22" s="1"/>
       <c r="M22" s="7" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="G23" s="6"/>
       <c r="M23" s="7" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="G24" s="6"/>
       <c r="M24" s="7" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:17">
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="M25" s="13" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -7185,10 +7690,10 @@
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="M26" s="13" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -7196,10 +7701,10 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:17">
       <c r="M27" s="13" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -7207,7 +7712,7 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:17">
       <c r="M28" s="13" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="N28" s="13"/>
       <c r="O28" s="13"/>
@@ -7216,7 +7721,7 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:17">
       <c r="M29" s="13" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="N29" s="13"/>
       <c r="O29" s="13"/>
@@ -7225,7 +7730,7 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:17">
       <c r="M30" s="13" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="N30" s="13"/>
       <c r="O30" s="13"/>
@@ -7234,40 +7739,40 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:17">
       <c r="M31" s="14" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:17">
       <c r="M32" s="14" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="11:17">
       <c r="M33" s="14" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="11:17">
       <c r="M34" s="7" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="N34" s="13"/>
       <c r="O34" s="13"/>
@@ -7276,7 +7781,7 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="11:17">
       <c r="M35" s="7" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="N35" s="13"/>
       <c r="O35" s="13"/>
@@ -7285,7 +7790,7 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="11:17">
       <c r="M36" s="7" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
@@ -7294,7 +7799,7 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="11:17">
       <c r="M37" s="7" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
@@ -7303,7 +7808,7 @@
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="11:17">
       <c r="M38" s="13" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
@@ -7312,10 +7817,10 @@
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="11:17">
       <c r="M39" s="13" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="N39" s="13" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
@@ -7323,10 +7828,10 @@
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="11:17">
       <c r="M40" s="13" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -7335,10 +7840,10 @@
     <row r="41" ht="16.5" customHeight="1" spans="11:17">
       <c r="K41" s="1"/>
       <c r="M41" s="13" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="N41" s="13" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
@@ -7347,10 +7852,10 @@
     <row r="42" ht="16.5" customHeight="1" spans="11:17">
       <c r="K42" s="1"/>
       <c r="M42" s="7" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -7359,10 +7864,10 @@
     <row r="43" ht="16.5" customHeight="1" spans="11:17">
       <c r="K43" s="1"/>
       <c r="M43" s="7" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
@@ -7371,10 +7876,10 @@
     <row r="44" ht="16.5" customHeight="1" spans="11:17">
       <c r="K44" s="1"/>
       <c r="M44" s="7" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
@@ -7383,10 +7888,10 @@
     <row r="45" ht="16.5" customHeight="1" spans="11:17">
       <c r="K45" s="1"/>
       <c r="M45" s="7" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="N45" s="13" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="O45" s="13"/>
       <c r="P45" s="13"/>
@@ -7395,10 +7900,10 @@
     <row r="46" ht="16.5" customHeight="1" spans="11:17">
       <c r="K46" s="1"/>
       <c r="M46" s="7" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="N46" s="13" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="O46" s="13"/>
       <c r="P46" s="13"/>
@@ -7407,10 +7912,10 @@
     <row r="47" ht="16.5" customHeight="1" spans="11:17">
       <c r="K47" s="1"/>
       <c r="M47" s="7" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="N47" s="13" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="O47" s="13"/>
       <c r="P47" s="13"/>
@@ -7419,10 +7924,10 @@
     <row r="48" ht="16.5" customHeight="1" spans="11:17">
       <c r="K48" s="1"/>
       <c r="M48" s="7" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
@@ -7431,10 +7936,10 @@
     <row r="49" ht="16.5" customHeight="1" spans="6:17">
       <c r="K49" s="1"/>
       <c r="M49" s="7" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
@@ -7443,10 +7948,10 @@
     <row r="50" ht="16.5" customHeight="1" spans="6:17">
       <c r="K50" s="1"/>
       <c r="M50" s="7" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
@@ -7455,10 +7960,10 @@
     <row r="51" ht="16.5" customHeight="1" spans="6:17">
       <c r="K51" s="1"/>
       <c r="M51" s="7" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="N51" s="13" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
       <c r="O51" s="13"/>
       <c r="P51" s="13"/>
@@ -7467,10 +7972,10 @@
     <row r="52" ht="16.5" customHeight="1" spans="6:17">
       <c r="K52" s="1"/>
       <c r="M52" s="7" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
@@ -7479,10 +7984,10 @@
     <row r="53" ht="16.5" customHeight="1" spans="6:17">
       <c r="K53" s="1"/>
       <c r="M53" s="7" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="N53" s="13" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
@@ -7501,7 +8006,7 @@
     </row>
     <row r="57" ht="16.5" customHeight="1" spans="6:17">
       <c r="F57" s="13" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
@@ -7514,7 +8019,7 @@
     </row>
     <row r="58" ht="16.5" customHeight="1" spans="6:17">
       <c r="F58" s="13" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
@@ -7527,7 +8032,7 @@
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="6:17">
       <c r="F59" s="13" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
@@ -7540,7 +8045,7 @@
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="6:17">
       <c r="F60" s="13" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
@@ -7553,7 +8058,7 @@
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="6:17">
       <c r="F61" s="13" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
@@ -7566,7 +8071,7 @@
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="6:17">
       <c r="F62" s="13" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
@@ -7579,7 +8084,7 @@
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="6:17">
       <c r="F63" s="13" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
@@ -7592,7 +8097,7 @@
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="6:17">
       <c r="F64" s="13" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="G64" s="13"/>
       <c r="H64" s="13"/>
@@ -7605,7 +8110,7 @@
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="6:14">
       <c r="F65" s="13" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="G65" s="13"/>
       <c r="H65" s="13"/>
@@ -7618,7 +8123,7 @@
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="6:14">
       <c r="F66" s="13" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="G66" s="13"/>
       <c r="H66" s="13"/>
@@ -7631,7 +8136,7 @@
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="6:14">
       <c r="F67" s="13" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="G67" s="13"/>
       <c r="H67" s="13"/>
@@ -7644,7 +8149,7 @@
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="6:14">
       <c r="F68" s="13" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="G68" s="13"/>
       <c r="H68" s="13"/>
@@ -7657,7 +8162,7 @@
     </row>
     <row r="69" ht="16.5" customHeight="1" spans="6:14">
       <c r="F69" s="13" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="G69" s="13"/>
       <c r="H69" s="13"/>
@@ -7681,10 +8186,10 @@
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="6:14">
       <c r="F71" s="13" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
@@ -7696,10 +8201,10 @@
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="6:14">
       <c r="F72" s="13" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -7711,10 +8216,10 @@
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="6:14">
       <c r="F73" s="13" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
@@ -7726,7 +8231,7 @@
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="6:14">
       <c r="F74" s="13" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
@@ -7739,7 +8244,7 @@
     </row>
     <row r="75" ht="16.5" customHeight="1" spans="6:14">
       <c r="F75" s="13" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
@@ -7752,7 +8257,7 @@
     </row>
     <row r="76" ht="16.5" customHeight="1" spans="6:14">
       <c r="F76" s="13" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="G76" s="13"/>
       <c r="H76" s="13"/>
@@ -7765,7 +8270,7 @@
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="6:14">
       <c r="F77" s="13" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="G77" s="13"/>
       <c r="H77" s="13"/>
@@ -7778,7 +8283,7 @@
     </row>
     <row r="78" ht="16.5" customHeight="1" spans="6:14">
       <c r="F78" s="13" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="G78" s="13"/>
       <c r="H78" s="13"/>
@@ -7791,7 +8296,7 @@
     </row>
     <row r="79" ht="16.5" customHeight="1" spans="6:14">
       <c r="F79" s="13" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="G79" s="13"/>
       <c r="H79" s="13"/>
@@ -7804,7 +8309,7 @@
     </row>
     <row r="80" ht="16.5" customHeight="1" spans="6:14">
       <c r="F80" s="7" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
@@ -7817,7 +8322,7 @@
     </row>
     <row r="81" ht="16.5" customHeight="1" spans="6:14">
       <c r="F81" s="7" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="G81" s="13"/>
       <c r="H81" s="13"/>
@@ -7830,7 +8335,7 @@
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="6:14">
       <c r="F82" s="7" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="G82" s="13"/>
       <c r="H82" s="13"/>
@@ -7843,7 +8348,7 @@
     </row>
     <row r="83" ht="16.5" customHeight="1" spans="6:14">
       <c r="F83" s="7" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="G83" s="13"/>
       <c r="H83" s="13"/>
@@ -7856,7 +8361,7 @@
     </row>
     <row r="84" ht="16.5" customHeight="1" spans="6:14">
       <c r="F84" s="13" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="G84" s="13"/>
       <c r="H84" s="13"/>
@@ -7869,10 +8374,10 @@
     </row>
     <row r="85" ht="16.5" customHeight="1" spans="6:14">
       <c r="F85" s="13" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="H85" s="13"/>
       <c r="I85" s="13"/>
@@ -7884,10 +8389,10 @@
     </row>
     <row r="86" ht="16.5" customHeight="1" spans="6:14">
       <c r="F86" s="13" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
@@ -7899,10 +8404,10 @@
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="6:14">
       <c r="F87" s="13" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="H87" s="13"/>
       <c r="I87" s="13"/>
@@ -7914,10 +8419,10 @@
     </row>
     <row r="88" ht="16.5" customHeight="1" spans="6:14">
       <c r="F88" s="7" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="H88" s="13"/>
       <c r="I88" s="13"/>
@@ -7929,10 +8434,10 @@
     </row>
     <row r="89" ht="16.5" customHeight="1" spans="6:14">
       <c r="F89" s="7" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="H89" s="13"/>
       <c r="I89" s="13"/>
@@ -7944,10 +8449,10 @@
     </row>
     <row r="90" ht="16.5" customHeight="1" spans="6:14">
       <c r="F90" s="7" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
@@ -7959,10 +8464,10 @@
     </row>
     <row r="91" ht="16.5" customHeight="1" spans="6:14">
       <c r="F91" s="7" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="H91" s="13"/>
       <c r="I91" s="13"/>
@@ -7974,10 +8479,10 @@
     </row>
     <row r="92" ht="16.5" customHeight="1" spans="6:14">
       <c r="F92" s="7" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="H92" s="13"/>
       <c r="I92" s="13"/>
@@ -7989,10 +8494,10 @@
     </row>
     <row r="93" ht="16.5" customHeight="1" spans="6:14">
       <c r="F93" s="7" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
@@ -8004,10 +8509,10 @@
     </row>
     <row r="94" ht="16.5" customHeight="1" spans="6:14">
       <c r="F94" s="7" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13"/>
@@ -8019,10 +8524,10 @@
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="6:14">
       <c r="F95" s="7" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="H95" s="13"/>
       <c r="I95" s="13"/>
@@ -8034,10 +8539,10 @@
     </row>
     <row r="96" ht="16.5" customHeight="1" spans="6:14">
       <c r="F96" s="7" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="H96" s="13"/>
       <c r="I96" s="13"/>
@@ -8049,10 +8554,10 @@
     </row>
     <row r="97" ht="16.5" customHeight="1" spans="6:14">
       <c r="F97" s="7" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
       <c r="H97" s="13"/>
       <c r="I97" s="13"/>
@@ -8064,10 +8569,10 @@
     </row>
     <row r="98" ht="16.5" customHeight="1" spans="6:14">
       <c r="F98" s="7" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="H98" s="13"/>
       <c r="I98" s="13"/>
@@ -8079,10 +8584,10 @@
     </row>
     <row r="99" ht="16.5" customHeight="1" spans="6:14">
       <c r="F99" s="7" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
